--- a/public/sample/medicines-sample.xlsx
+++ b/public/sample/medicines-sample.xlsx
@@ -413,8 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -456,25 +456,30 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>batch_number</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>expiry_date</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>supplier_phone</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>supplier_email</t>
         </is>
@@ -502,25 +507,30 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>PARA-001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>2027-12-31</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Pain and fever</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>ABC Supplier</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>+251911000000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>abc@example.com</t>
         </is>
@@ -548,25 +558,30 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>AMOX-002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>2027-06-30</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Antibiotic</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>HealthMed PLC</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>+251922000000</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>sales@healthmed.et</t>
         </is>
@@ -594,25 +609,30 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>ORS-003</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>2028-01-31</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Dehydration / diarrhea</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Care Supply</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>+251933000000</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
